--- a/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericType.xlsx
+++ b/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericType.xlsx
@@ -775,7 +775,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -785,7 +785,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericType.xlsx
+++ b/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericType.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21600"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="numeric" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
   <si>
     <t>这是id</t>
   </si>
@@ -511,30 +511,6 @@
   </si>
   <si>
     <t>技能持续时间</t>
-  </si>
-  <si>
-    <t>SkillChildNum</t>
-  </si>
-  <si>
-    <t>子技能物体个数</t>
-  </si>
-  <si>
-    <t>SkillChildAttackRange</t>
-  </si>
-  <si>
-    <t>子技能攻击范围</t>
-  </si>
-  <si>
-    <t>SkillChildDuration</t>
-  </si>
-  <si>
-    <t>子技能持续时间</t>
-  </si>
-  <si>
-    <t>SkillChildMoveSpeed</t>
-  </si>
-  <si>
-    <t>子技能移动速度</t>
   </si>
   <si>
     <t>对局资源相关</t>
@@ -764,7 +740,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -775,7 +751,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -785,7 +761,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1629,7 +1605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:XFD38"/>
+  <dimension ref="A1:XFD34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.5" style="6" customWidth="1"/>
@@ -83880,7 +83856,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F19" s="6">
         <v>0</v>
@@ -83985,101 +83961,101 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="6">
-        <v>300005</v>
-      </c>
-      <c r="B26" s="7" t="s">
+    <row r="26" s="3" customFormat="1" spans="1:8">
+      <c r="A26" s="2"/>
+      <c r="B26" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="12"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="6">
+        <v>400001</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="6">
-        <v>300006</v>
-      </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="6"/>
+      <c r="E27" s="6">
+        <v>1</v>
+      </c>
       <c r="F27" s="6">
         <v>0</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="7"/>
     </row>
-    <row r="28" customFormat="1" spans="1:8">
+    <row r="28" spans="1:6">
       <c r="A28" s="6">
-        <v>300007</v>
+        <v>400002</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>69</v>
+      <c r="D28" s="6" t="s">
+        <v>21</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>59</v>
+      <c r="E28" s="6">
+        <v>1</v>
       </c>
-      <c r="E28" s="6"/>
       <c r="F28" s="6">
         <v>0</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="7"/>
     </row>
-    <row r="29" customFormat="1" spans="1:8">
+    <row r="29" spans="1:6">
       <c r="A29" s="6">
-        <v>300008</v>
+        <v>400003</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="6"/>
+      <c r="E29" s="6">
+        <v>1</v>
+      </c>
       <c r="F29" s="6">
         <v>0</v>
       </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="7"/>
     </row>
-    <row r="30" s="3" customFormat="1" spans="1:8">
-      <c r="A30" s="2"/>
-      <c r="B30" s="11" t="s">
+    <row r="30" spans="1:6">
+      <c r="A30" s="6">
+        <v>400004</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="12"/>
+      <c r="D30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6">
-        <v>400001</v>
+        <v>400005</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>73</v>
@@ -84097,38 +84073,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="6">
-        <v>400002</v>
-      </c>
-      <c r="B32" s="7" t="s">
+    <row r="32" s="5" customFormat="1" spans="1:8">
+      <c r="A32" s="2"/>
+      <c r="B32" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="6">
-        <v>1</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0</v>
-      </c>
+      <c r="C32" s="11"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="11"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6">
-        <v>400003</v>
+        <v>500001</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="E33" s="6">
         <v>1</v>
@@ -84139,7 +84107,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6">
-        <v>400004</v>
+        <v>500002</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>79</v>
@@ -84148,84 +84116,12 @@
         <v>80</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="E34" s="6">
         <v>1</v>
       </c>
       <c r="F34" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="6">
-        <v>400005</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="6">
-        <v>1</v>
-      </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="5" customFormat="1" spans="1:8">
-      <c r="A36" s="2"/>
-      <c r="B36" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="6">
-        <v>500001</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1</v>
-      </c>
-      <c r="F37" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="6">
-        <v>500002</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" s="6">
-        <v>1</v>
-      </c>
-      <c r="F38" s="6">
         <v>0</v>
       </c>
     </row>

--- a/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericType.xlsx
+++ b/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericType.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>这是id</t>
   </si>
@@ -546,6 +546,12 @@
     <t>对局等级</t>
   </si>
   <si>
+    <t>BattleDuration</t>
+  </si>
+  <si>
+    <t>对局持续时间</t>
+  </si>
+  <si>
     <t>对局功能开关</t>
   </si>
   <si>
@@ -740,13 +746,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1605,7 +1611,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:XFD34"/>
+  <dimension ref="A1:XFD35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.5" style="6" customWidth="1"/>
@@ -84073,55 +84079,77 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" s="5" customFormat="1" spans="1:8">
-      <c r="A32" s="2"/>
-      <c r="B32" s="11" t="s">
+    <row r="32" customFormat="1" spans="1:8">
+      <c r="A32" s="6">
+        <v>400006</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="6">
-        <v>500001</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" s="5" customFormat="1" spans="1:8">
+      <c r="A33" s="2"/>
+      <c r="B33" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="6">
-        <v>1</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="11"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="E34" s="6">
         <v>1</v>
       </c>
       <c r="F34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="6">
+        <v>500002</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6">
         <v>0</v>
       </c>
     </row>
